--- a/storage/app/private/CLIENTES/BERNARDO/Bitacora_BERNARDO_JUNIO-2026.xlsx
+++ b/storage/app/private/CLIENTES/BERNARDO/Bitacora_BERNARDO_JUNIO-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\ComandosBitacora\storage\app\private\CLIENTES\BERNARDO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6AE7F46-C144-4CA3-AC03-AE28AAE4247E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBE8ED5C-7DD9-4DBF-92BB-906C565B4840}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -198,7 +198,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -220,9 +220,6 @@
     <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -685,20 +682,19 @@
   <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="59.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="45.88671875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="9.33203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
@@ -724,7 +720,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="6"/>
-      <c r="C5" s="13"/>
+      <c r="C5" s="5"/>
       <c r="D5" s="7"/>
       <c r="E5" s="6"/>
     </row>

--- a/storage/app/private/CLIENTES/BERNARDO/Bitacora_BERNARDO_JUNIO-2026.xlsx
+++ b/storage/app/private/CLIENTES/BERNARDO/Bitacora_BERNARDO_JUNIO-2026.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBE8ED5C-7DD9-4DBF-92BB-906C565B4840}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Facturas" sheetId="1" r:id="rId1"/>
